--- a/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h2_5s.xlsx
+++ b/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h2_5s.xlsx
@@ -121,7 +121,7 @@
     <t>sound: engine(0-60), sound: engine(180-240), sound: gunshot_or_explosion(120-180), visual: gunshot_visible(120-120), visual: physical_altercation(96-96), visual: running(144-144), visual: running(120-120), visual: suspicious_near_vehicle(48-96), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(72-72), visual: suspicious_near_vehicle(216-240), visual: suspicious_near_vehicle(24-96), visual: suspicious_near_vehicle(168-192), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
-    <t>sound: gunshot_or_explosion(0-60), sound: engine(60-240), visual: explosion_visible(24-240), visual: running(24-48), visual: running(168-192), visual: running(72-144)</t>
+    <t>sound: gunshot_or_explosion(0-60), sound: engine(60-120), sound: engine(180-240), visual: explosion_visible(24-240), visual: running(24-48), visual: running(168-192), visual: running(72-144)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-60), sound: engine(120-240), visual: explosion_visible(48-240), visual: running(144-168), visual: running(96-96), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(24-120), visual: suspicious_near_vehicle(240-240)</t>

--- a/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h2_5s.xlsx
+++ b/data/analysis_gemini_3_6_flash_panns/multimodal_event_eval_gemini_3_6_flash_panns_w2_5s_h2_5s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>sound: engine(120-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
   </si>
   <si>
     <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-24), visual: suspicious_near_vehicle(48-144)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1457,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1494,6 +1497,23 @@
         <v>43</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1535,7 +1555,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1643,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1667,7 +1687,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1705,13 +1725,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1799,7 +1819,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1843,7 +1863,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
